--- a/reference/The_Ballroom_Array_Weights_v6.xlsx
+++ b/reference/The_Ballroom_Array_Weights_v6.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Designer</t>
   </si>
   <si>
-    <t xml:space="preserve">Mark Hughes</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">Load over people?</t>
@@ -5895,7 +5895,7 @@
       <c r="F7" s="48"/>
       <c r="G7" s="47" t="str">
         <f aca="false">IF(Calc!B3="","",Calc!B3)</f>
-        <v>Mark Hughes</v>
+        <v/>
       </c>
       <c r="H7" s="47"/>
     </row>
